--- a/AAII_Financials/Quarterly/ZIM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ZIM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="92">
   <si>
     <t>ZIM</t>
   </si>
@@ -656,427 +656,440 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="33" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="34" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AF7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AG7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>1780700</v>
+      </c>
+      <c r="E8" s="3">
         <v>1396500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1484700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1777200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1635700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2006600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2167600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2765200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1932600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1562000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1205300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1273000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1309600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1374300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2188900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3227500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3428800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3716400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3466400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3136000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2382000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1744300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1360800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1012500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>795100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>827300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>841900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1630500</v>
       </c>
-      <c r="AE8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>1213600</v>
+      </c>
+      <c r="E9" s="3">
         <v>1031700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1086800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1113400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1098000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1162600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1131300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1167800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1133300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1080800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>963100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1008400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>973900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>939700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1514900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1623300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1593900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1402700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1271400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1222500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1159500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1008800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>883400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>785300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>692600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>750200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>766600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1519900</v>
       </c>
-      <c r="AE9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>567100</v>
+      </c>
+      <c r="E10" s="3">
         <v>364800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>397900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>663800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>537700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>844000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1036300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1597400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>799300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>481200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>242200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>264600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>335700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>434600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>674000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1604200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1834900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2313700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2195000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1913500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1222500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>735500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>477400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>227200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>102500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>77100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>75300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>110600</v>
       </c>
-      <c r="AE10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1110,8 +1123,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1205,8 +1219,11 @@
       <c r="AG12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1300,47 +1317,50 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
         <v>-174600</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3">
         <v>-43900</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3">
         <v>63600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>2034900</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1353,8 +1373,8 @@
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
@@ -1395,53 +1415,56 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>312100</v>
+      </c>
+      <c r="E15" s="3">
         <v>307600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>306300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>325500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>316900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>310800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>305300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>292100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>275100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>257700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>237000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>417400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>414900</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>380500</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1490,8 +1513,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1522,198 +1548,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1631500</v>
+      </c>
+      <c r="E17" s="3">
         <v>1410200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1514700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1513700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1484000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1539900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1552300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1529600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1462400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1393300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1238700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1511500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1474900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1387800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1612300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1704700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1679200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1478500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1354600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1277000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1224900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1060900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>921300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>823700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>726300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>782700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>796300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1567800</v>
       </c>
-      <c r="AE17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>149200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-13700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-30000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>263500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>151700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>466700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>615300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1235600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>470200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>168700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-33400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-238500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-165300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-13500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>576600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1522800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1749600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2237900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2111800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1859000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1157100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>683400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>439500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>188800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>68800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>44600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>45600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>62700</v>
       </c>
-      <c r="AE18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1747,243 +1780,250 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E20" s="3">
         <v>4600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>16000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>4100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>2500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>2400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-23400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>2100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>22500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>2300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>2500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-18700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-8400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-13200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-19300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-29200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-38100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-45000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-39400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-67700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-40700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-39100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-41800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-37700</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-74700</v>
       </c>
-      <c r="AE20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>456400</v>
+      </c>
+      <c r="E21" s="3">
         <v>289300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>260300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>584900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>466100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>775100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>944000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1526900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>743400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>424300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>181100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>176600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>247100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>366600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>946500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1894600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2073700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>2508800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>2331100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>2041800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1288100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>777600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>465100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>222400</v>
       </c>
-      <c r="AA21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB21" s="3">
+      <c r="AB21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC21" s="3">
         <v>72900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>76100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>95200</v>
       </c>
-      <c r="AE21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>107700</v>
+      </c>
+      <c r="E22" s="3">
         <v>112200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>100300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>121400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>129600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>123800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>121200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>121600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>115900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>109000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>42100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>101500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>142000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>95200</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
       <c r="R22" s="3">
         <v>0</v>
       </c>
@@ -2032,198 +2072,207 @@
       <c r="AG22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>60700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-98200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>56400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>172300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>49300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>380500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>600800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1133000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>374900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>96300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-137100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-2341600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-272100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-64700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>557900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1514400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1736400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2218600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>2082500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1820900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1112000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>644000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>371800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>148100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>29700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>2800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>8000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-12000</v>
       </c>
-      <c r="AE23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E24" s="3">
         <v>-11900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>18100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>48900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>25600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>84400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>38100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>6800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>4200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>9500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-71100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-59400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-6600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>141400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>348700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>400600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>507600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>374100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>358000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>223800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>54400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>5400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>3700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>4400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>3000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>7200</v>
       </c>
-      <c r="AE24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2317,198 +2366,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>64100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-86300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>38300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>123400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>23700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>296100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>562700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1126200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>372800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>92100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-146600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-2270500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-212700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-58100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>416500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1165700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1335800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1711000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1708400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1462900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>888200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>589600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>366400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>144400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>25300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>4900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-19200</v>
       </c>
-      <c r="AE26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>63500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-86000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>38100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>123000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>22800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>295300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>561500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1124600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>371300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>90300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-148400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-2272600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-215100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-59500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>414200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1163300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1333100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1708800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1705100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1461100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>886500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>587600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>365000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>142400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>24000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>3800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-21500</v>
       </c>
-      <c r="AE27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2602,8 +2660,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2697,8 +2758,11 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2792,8 +2856,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2887,198 +2954,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="E32" s="3">
         <v>-4600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-16000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-4100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-2500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-2400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>23400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-2100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-22500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-2300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-2500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>18700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>8400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>13200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>19300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>29200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>38100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>45000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>39400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>67700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>40700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>39100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>41800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>37700</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>74700</v>
       </c>
-      <c r="AE32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>63500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-86000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>38100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>123000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>22800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>295300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>561500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1124600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>371300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>90300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-148400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-2272600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-215100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-59500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>414200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1163300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1333100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1708800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1705100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1461100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>886500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>587600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>365000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>142400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>24000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>3800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-21500</v>
       </c>
-      <c r="AE33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3172,203 +3248,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>63500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-86000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>38100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>123000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>22800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>295300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>561500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1124600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>371300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>90300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-148400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-2272600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-215100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-59500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>414200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1163300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1333100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1708800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1705100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1461100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>886500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>587600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>365000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>142400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>24000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>3800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-21500</v>
       </c>
-      <c r="AE35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AF38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AG38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3402,8 +3487,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3437,89 +3523,90 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1037100</v>
+      </c>
+      <c r="E41" s="3">
         <v>921600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1051700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1299000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1187100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1546100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1314700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1548700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>889800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>687900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>921500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>912100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1040300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1892600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1022100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1285700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>946800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2727200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1543300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2455000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1545300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1188400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>570400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>350300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>202800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>182800</v>
       </c>
-      <c r="AC41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3532,89 +3619,92 @@
       <c r="AG41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>600900</v>
+      </c>
+      <c r="E42" s="3">
         <v>705700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>735100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>651100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>585700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>765400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>800400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>766600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>699100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>744800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>874100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>918600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>863000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>1060200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>2233100</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>1871700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>2358900</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>2092400</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>2144500</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>345100</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>46800</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>63000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>59000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>58900</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>61400</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>59000</v>
       </c>
-      <c r="AC42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3627,89 +3717,92 @@
       <c r="AG42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>992700</v>
+      </c>
+      <c r="E43" s="3">
         <v>720900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>653500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>650100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>794600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>760000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>908500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1062500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1030900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>868000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>562500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>644300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>671000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>695300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>825700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1088700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1346200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1386400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1278100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1234200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>963300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>700400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>520000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>358200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>279500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>317100</v>
       </c>
-      <c r="AC43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3722,89 +3815,92 @@
       <c r="AG43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>223100</v>
+      </c>
+      <c r="E44" s="3">
         <v>206600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>167800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>182000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>199300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>217500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>212200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>208400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>187700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>197300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>179300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>156400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>174100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>189100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>190700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>225700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>216200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>173800</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>119000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>107300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>99800</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>86300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>52200</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>47400</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>43500</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>60300</v>
       </c>
-      <c r="AC44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3817,8 +3913,11 @@
       <c r="AG44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3861,8 +3960,8 @@
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R45" s="3">
         <v>0</v>
@@ -3885,21 +3984,21 @@
       <c r="X45" s="3">
         <v>0</v>
       </c>
-      <c r="Y45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z45" s="3">
+      <c r="Y45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA45" s="3">
         <v>8700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>8100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>11600</v>
       </c>
-      <c r="AC45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3912,89 +4011,92 @@
       <c r="AG45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2853800</v>
+      </c>
+      <c r="E46" s="3">
         <v>2554800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2630600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2782200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2766700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3289000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3260900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3586200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2807500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2498000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2571400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2631400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2748400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3837200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>4271600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>4471800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>4868100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>6379800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>5084900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>4141600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>2655100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>2038100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1201600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>823400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>595300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>630800</v>
       </c>
-      <c r="AC46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD46" s="3" t="s">
         <v>3</v>
       </c>
@@ -4007,89 +4109,92 @@
       <c r="AG46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>989400</v>
+      </c>
+      <c r="E47" s="3">
         <v>1002300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1080300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1128200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1170900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1131000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1106300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>870600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>800400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>844300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>935100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1279400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1383500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1367300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1507300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1449800</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>778300</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>427700</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>288400</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>25400</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>23900</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>22300</v>
-      </c>
-      <c r="Y47" s="3">
-        <v>18600</v>
       </c>
       <c r="Z47" s="3">
         <v>18600</v>
       </c>
       <c r="AA47" s="3">
+        <v>18600</v>
+      </c>
+      <c r="AB47" s="3">
         <v>17000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>16500</v>
       </c>
-      <c r="AC47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD47" s="3" t="s">
         <v>3</v>
       </c>
@@ -4102,89 +4207,92 @@
       <c r="AG47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6587700</v>
+      </c>
+      <c r="E48" s="3">
         <v>6781700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>7018800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>6802700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>6992100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>6898300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6840800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6381700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5915700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5399300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4636000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4072200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>6339500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>6115600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>5751200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>5988200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>5764400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>5435700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>4392600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>3605600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2854600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2029800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1536000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1290000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1222300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>1212800</v>
       </c>
-      <c r="AC48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD48" s="3" t="s">
         <v>3</v>
       </c>
@@ -4197,89 +4305,92 @@
       <c r="AG48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>108000</v>
+      </c>
+      <c r="E49" s="3">
         <v>108500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>109400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>108600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>109900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>110300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>109800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>107600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>105700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>104800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>102000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>93300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>98100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>95100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>92900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>82500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>79400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>77500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>73800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>68400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>67400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>66800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>66500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>64000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>64700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>64900</v>
       </c>
-      <c r="AC49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD49" s="3" t="s">
         <v>3</v>
       </c>
@@ -4292,8 +4403,11 @@
       <c r="AG49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4387,8 +4501,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4482,52 +4599,55 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>117300</v>
+      </c>
+      <c r="E52" s="3">
         <v>121600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>159800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>44800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>50400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>55500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>64200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>69900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>76600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>82700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>98900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>105500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>111600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>113900</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>2300</v>
       </c>
       <c r="R52" s="3">
         <v>2300</v>
@@ -4539,32 +4659,32 @@
         <v>2300</v>
       </c>
       <c r="U52" s="3">
+        <v>2300</v>
+      </c>
+      <c r="V52" s="3">
         <v>2100</v>
-      </c>
-      <c r="V52" s="3">
-        <v>1500</v>
       </c>
       <c r="W52" s="3">
         <v>1500</v>
       </c>
       <c r="X52" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Y52" s="3">
         <v>1600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1500</v>
-      </c>
-      <c r="Z52" s="3">
-        <v>1200</v>
       </c>
       <c r="AA52" s="3">
         <v>1200</v>
       </c>
       <c r="AB52" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AC52" s="3">
         <v>1000</v>
       </c>
-      <c r="AC52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4577,8 +4697,11 @@
       <c r="AG52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4672,89 +4795,92 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>10665200</v>
+      </c>
+      <c r="E54" s="3">
         <v>10577700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>11008100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>10874400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>11097700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>11491700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>11389500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>11018500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>9708400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>8931600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>8346000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>8191400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>10683600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>11532000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>11625300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>11994600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>11492500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>12323000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>9841800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>7842400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>5602500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>4158600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2824200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>2197200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1900600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1926100</v>
       </c>
-      <c r="AC54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4767,8 +4893,11 @@
       <c r="AG54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4802,8 +4931,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4837,89 +4967,90 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>714400</v>
+      </c>
+      <c r="E57" s="3">
         <v>703700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>467100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>609600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>641700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1137800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>508300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>668300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>610300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>612200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>414600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>554600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>561800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>590800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>896200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>846600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>901300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2946200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1086200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1052300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>944800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>538700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>398900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>396700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>375300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>422400</v>
       </c>
-      <c r="AC57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4932,89 +5063,92 @@
       <c r="AG57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1079200</v>
+      </c>
+      <c r="E58" s="3">
         <v>1114500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1139400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1175600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1215500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1282900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1369500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1492000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1530100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1582900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1692900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1716100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1570100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1572700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1476900</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1524500</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1457100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1353200</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1023700</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>907600</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>793700</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>645900</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>500700</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>392400</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>359800</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>355600</v>
       </c>
-      <c r="AC58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD58" s="3" t="s">
         <v>3</v>
       </c>
@@ -5027,89 +5161,92 @@
       <c r="AG58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>501800</v>
+      </c>
+      <c r="E59" s="3">
         <v>331800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>398500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>348000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>447300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>373100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>576600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>526800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>563000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>356500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>305200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>265600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>261800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1016300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>289100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>461700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>608300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>628200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>646700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>665000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>481200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>321300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>251900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>186900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>137600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>148300</v>
       </c>
-      <c r="AC59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD59" s="3" t="s">
         <v>3</v>
       </c>
@@ -5122,89 +5259,92 @@
       <c r="AG59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2295400</v>
+      </c>
+      <c r="E60" s="3">
         <v>2150000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2134100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2133200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2304500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2793800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2611200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2687100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2703400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2551600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2518100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2536300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2393700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3179800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2662200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2832800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2966700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>4927600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2756600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2625000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2219700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1505900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1151500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>975900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>872800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>926300</v>
       </c>
-      <c r="AC60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD60" s="3" t="s">
         <v>3</v>
       </c>
@@ -5217,89 +5357,92 @@
       <c r="AG60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4233400</v>
+      </c>
+      <c r="E61" s="3">
         <v>4363800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4598800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4484800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>4699700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>4595200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4660500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4352100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4065300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3783400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3317700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3031300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3313400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3081200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2870600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>3160100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>3093800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2955500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2299500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1892600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1557800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1495300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1331300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1254900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1207500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1183700</v>
       </c>
-      <c r="AC61" s="3">
-        <v>0</v>
-      </c>
       <c r="AD61" s="3">
         <v>0</v>
       </c>
@@ -5312,8 +5455,11 @@
       <c r="AG61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5356,45 +5502,45 @@
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R62" s="3">
         <v>196600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>184400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>183800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>179700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>186200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>149600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>106600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>97400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>67000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>61500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>60300</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>68300</v>
       </c>
-      <c r="AC62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5407,8 +5553,11 @@
       <c r="AG62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5502,8 +5651,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5597,8 +5749,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5692,89 +5847,92 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>6780600</v>
+      </c>
+      <c r="E66" s="3">
         <v>6749600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>6982500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>6854200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>7196000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>7527800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>7346800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>7087800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>6816900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>6386200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5888000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5620000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5828500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>6449200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>5735700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>6184100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>6250500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>8067100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>5249800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>4673700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>3889100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3102400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>2557000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2297800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>2144700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>2183800</v>
       </c>
-      <c r="AC66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5787,8 +5945,11 @@
       <c r="AG66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5822,8 +5983,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5917,8 +6079,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6012,8 +6177,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6107,8 +6275,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6202,89 +6373,92 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2986700</v>
+      </c>
+      <c r="E72" s="3">
         <v>2927600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>3137300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>3133600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>3014200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>3076600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>3155500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>3042200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2007200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1659300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1570900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1682800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>3967400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>4190400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>5889600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>5810500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>5242000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>4255900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>4592000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>3168700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>1713400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>1056300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>267200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-100700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-244200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-257800</v>
       </c>
-      <c r="AC72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6297,8 +6471,11 @@
       <c r="AG72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6392,8 +6569,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6487,8 +6667,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6582,89 +6765,92 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3881200</v>
+      </c>
+      <c r="E76" s="3">
         <v>3824200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4020900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4015500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3897400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3957900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4036900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3925900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2889100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2541300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2454700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2567600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4853100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>5081700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>5889600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>5810500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>5242000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>4255900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>4592000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>3168700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1713400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1056300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>267300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>-100600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>-244200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>-257700</v>
       </c>
-      <c r="AC76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6677,8 +6863,11 @@
       <c r="AG76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6772,203 +6961,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AF80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AG80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>63500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-86000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>38100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>123000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>22800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>295300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>561500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1124600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>371300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>90300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-148400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-2272600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-215100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-59500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>414200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1163300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1333100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1708800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1705100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1461100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>886500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>587600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>365000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>142400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>24000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>3800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-21500</v>
       </c>
-      <c r="AE81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7002,103 +7200,107 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>323100</v>
+      </c>
+      <c r="E83" s="3">
         <v>315900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>295400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>295000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>278000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>260600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>228100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>423800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>421500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>387200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>377100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>380200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>337300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>290200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>388600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>380200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>337300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>290200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>248600</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>220900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>176100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>133600</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>93300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>74300</v>
       </c>
-      <c r="AA83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB83" s="3">
+      <c r="AB83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC83" s="3">
         <v>70100</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>68200</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>107200</v>
       </c>
-      <c r="AE83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7192,8 +7394,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7287,8 +7492,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7382,8 +7590,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7477,8 +7688,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7572,103 +7786,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>394600</v>
+      </c>
+      <c r="E89" s="3">
         <v>262700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>375100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>628400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>441300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>854700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1152300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1497500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>776800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>326100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>162200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>337600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>346600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>173600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1068600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1671600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1709900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1660000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>2004600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>2008300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1180600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>777400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>414400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>245100</v>
       </c>
-      <c r="AA89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB89" s="3">
+      <c r="AB89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC89" s="3">
         <v>89300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>157500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>123800</v>
       </c>
-      <c r="AE89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7702,56 +7922,57 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-11600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-31300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-48000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-67300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-24400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-78000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-73000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-50300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-66400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-24400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-40500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-13700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-25600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-35900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-345500</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
       <c r="S91" s="3">
         <v>0</v>
       </c>
@@ -7797,8 +8018,11 @@
       <c r="AG91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7892,8 +8116,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7987,103 +8214,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>113100</v>
+      </c>
+      <c r="E94" s="3">
         <v>105400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-174300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-58500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>141200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-41700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-317100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-146200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>56400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>183700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>445800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-9100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>133600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>1206200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-435400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-255800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-693200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-260600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-2308000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-587200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-313300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-134600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-22100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-5300</v>
       </c>
-      <c r="AA94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB94" s="3">
+      <c r="AB94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC94" s="3">
         <v>-6700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>5500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>39200</v>
       </c>
-      <c r="AE94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8117,68 +8350,69 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3">
         <v>106100</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>37400</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>7200</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>471000</v>
       </c>
-      <c r="H96" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I96" s="3">
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3">
         <v>338500</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>111900</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>27700</v>
       </c>
-      <c r="L96" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
-      <c r="N96" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O96" s="3">
+      <c r="M96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P96" s="3">
         <v>769200</v>
       </c>
-      <c r="P96" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q96" s="3">
+      <c r="Q96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R96" s="3">
         <v>-354400</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-570300</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
       <c r="T96" s="3">
         <v>0</v>
       </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-299400</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
         <v>0</v>
       </c>
@@ -8212,8 +8446,11 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8307,8 +8544,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8402,8 +8642,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8497,289 +8740,301 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-389500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-498400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-449200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-457700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-944100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-582300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1064500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-696900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-629200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-740800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-599600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-451500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1332100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-509700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-904700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1067000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-2790000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-214700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-606900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-511200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-511300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-23600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-174300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-94100</v>
       </c>
-      <c r="AA100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB100" s="3">
+      <c r="AB100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC100" s="3">
         <v>-85200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-141700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-184400</v>
       </c>
-      <c r="AE100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E101" s="3">
         <v>700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-4700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>4500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-2100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-2600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>1000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-5200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>7900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-9900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-7100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>7900</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-9900</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-7100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-800</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-1400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-300</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>900</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-1200</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>2200</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>1700</v>
       </c>
-      <c r="AA101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB101" s="3">
+      <c r="AB101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC101" s="3">
         <v>800</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-1500</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-100</v>
       </c>
-      <c r="AE101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF101" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>115500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-130100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-247300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>111900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-359000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>231400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-234000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>658900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>201900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-233600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>9400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-128200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-852300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>870500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-263600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>338900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1780400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1183900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-911700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>909700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>356900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>618000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>220100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>147400</v>
       </c>
-      <c r="AA102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB102" s="3">
+      <c r="AB102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC102" s="3">
         <v>-1800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>19800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-21500</v>
       </c>
-      <c r="AE102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
